--- a/data/processed/positivacao/2025-08_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-08_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27337,7 +27337,7 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr"/>
@@ -38221,7 +38221,7 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr"/>
@@ -66229,7 +66229,7 @@
     <row r="2536">
       <c r="A2536" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2536" t="inlineStr"/>
@@ -67822,12 +67822,12 @@
       <c r="A2598" t="inlineStr"/>
       <c r="B2598" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 3 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 1.047,92
+          <t>Vendedor 1 - VENDEDOR 01: positivou 3 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 1.047,92
 Vendedor 18 - LOJA: positivou 297 cliente(s), não positivou 642 cliente(s) - Total vendido: R$ 79.382,63
-Vendedor 3 - FERNANDA: positivou 115 cliente(s), não positivou 303 cliente(s) - Total vendido: R$ 132.171,21
-Vendedor 4 - DANIELA: positivou 124 cliente(s), não positivou 507 cliente(s) - Total vendido: R$ 72.587,68
+Vendedor 3 - VENDEDOR 03: positivou 115 cliente(s), não positivou 303 cliente(s) - Total vendido: R$ 132.171,21
+Vendedor 4 - VENDEDOR 04: positivou 124 cliente(s), não positivou 507 cliente(s) - Total vendido: R$ 72.587,68
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 445 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2598" t="inlineStr"/>
